--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Back_Summary.xlsx
@@ -434,12 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -451,23 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.75417</v>
+        <v>17.67234</v>
       </c>
       <c r="D2" t="n">
-        <v>17.40811</v>
+        <v>17.40091</v>
       </c>
       <c r="E2" t="n">
-        <v>17.57585</v>
+        <v>17.52921</v>
       </c>
       <c r="F2" t="n">
-        <v>23.01231</v>
+        <v>44.92446</v>
       </c>
       <c r="G2" t="n">
-        <v>36.45951</v>
+        <v>0.05265</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.93917</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.67554</v>
+        <v>18.02661</v>
       </c>
       <c r="D3" t="n">
-        <v>16.89043</v>
+        <v>17.42339</v>
       </c>
       <c r="E3" t="n">
-        <v>17.3509</v>
+        <v>17.83402</v>
       </c>
       <c r="F3" t="n">
-        <v>22.90378</v>
+        <v>44.07444</v>
       </c>
       <c r="G3" t="n">
-        <v>36.54334</v>
+        <v>0.05354</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.94271</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.87809</v>
+        <v>17.87123</v>
       </c>
       <c r="D4" t="n">
-        <v>17.24396</v>
+        <v>17.37192</v>
       </c>
       <c r="E4" t="n">
-        <v>17.11996</v>
+        <v>17.67394</v>
       </c>
       <c r="F4" t="n">
-        <v>23.45898</v>
+        <v>43.91098</v>
       </c>
       <c r="G4" t="n">
-        <v>36.61111</v>
+        <v>0.05396</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.88247</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.29722</v>
+        <v>17.90238</v>
       </c>
       <c r="D5" t="n">
-        <v>17.24635</v>
+        <v>17.38402</v>
       </c>
       <c r="E5" t="n">
-        <v>17.29245</v>
+        <v>17.80717</v>
       </c>
       <c r="F5" t="n">
-        <v>23.28391</v>
+        <v>44.96372</v>
       </c>
       <c r="G5" t="n">
-        <v>36.30097</v>
+        <v>0.0523</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.96006</v>
       </c>
     </row>
     <row r="6">
@@ -542,20 +559,10 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>17.59417</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16.99941</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17.4638</v>
-      </c>
-      <c r="F6" t="n">
-        <v>22.74806</v>
-      </c>
-      <c r="G6" t="n">
-        <v>35.66507</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>scratched - not measurable</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -565,19 +572,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18.05244</v>
+        <v>17.85534</v>
       </c>
       <c r="D7" t="n">
-        <v>16.99074</v>
+        <v>17.47198</v>
       </c>
       <c r="E7" t="n">
-        <v>17.74807</v>
+        <v>17.6749</v>
       </c>
       <c r="F7" t="n">
-        <v>22.98194</v>
+        <v>45.69867</v>
       </c>
       <c r="G7" t="n">
-        <v>35.96702</v>
+        <v>0.05367</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.92586</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +597,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.3705</v>
+        <v>18.07855</v>
       </c>
       <c r="D8" t="n">
-        <v>17.04783</v>
+        <v>17.56627</v>
       </c>
       <c r="E8" t="n">
-        <v>17.67712</v>
+        <v>17.89274</v>
       </c>
       <c r="F8" t="n">
-        <v>23.08129</v>
+        <v>44.71143</v>
       </c>
       <c r="G8" t="n">
-        <v>36.56787</v>
+        <v>0.05363</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.9393</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +622,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.57548</v>
+        <v>18.14395</v>
       </c>
       <c r="D9" t="n">
-        <v>17.00093</v>
+        <v>17.39014</v>
       </c>
       <c r="E9" t="n">
-        <v>17.11248</v>
+        <v>17.6221</v>
       </c>
       <c r="F9" t="n">
-        <v>22.81662</v>
+        <v>44.22382</v>
       </c>
       <c r="G9" t="n">
-        <v>36.75859</v>
+        <v>0.05353</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.88856</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +647,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.97818</v>
+        <v>17.84161</v>
       </c>
       <c r="D10" t="n">
-        <v>17.10621</v>
+        <v>17.69576</v>
       </c>
       <c r="E10" t="n">
-        <v>17.20412</v>
+        <v>17.76975</v>
       </c>
       <c r="F10" t="n">
-        <v>23.19566</v>
+        <v>44.59484</v>
       </c>
       <c r="G10" t="n">
-        <v>36.46912</v>
+        <v>0.05374</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.92165</v>
       </c>
     </row>
     <row r="11">
@@ -664,17 +683,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -686,26 +700,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.88555</v>
+        <v>17.90173</v>
       </c>
       <c r="D12" t="n">
-        <v>17.73098</v>
+        <v>16.90049</v>
       </c>
       <c r="E12" t="n">
-        <v>17.33674</v>
+        <v>17.12422</v>
       </c>
       <c r="F12" t="n">
-        <v>44.47139</v>
+        <v>23.38022</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05289</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.93858</v>
+        <v>36.39043</v>
       </c>
     </row>
     <row r="13">
@@ -715,22 +726,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.68324</v>
+        <v>17.40778</v>
       </c>
       <c r="D13" t="n">
-        <v>17.5066</v>
+        <v>17.04976</v>
       </c>
       <c r="E13" t="n">
-        <v>17.51501</v>
+        <v>17.24009</v>
       </c>
       <c r="F13" t="n">
-        <v>44.28919</v>
+        <v>22.94615</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05406</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.85459</v>
+        <v>37.27745</v>
       </c>
     </row>
     <row r="14">
@@ -739,23 +747,25 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>re-measured</t>
+        </is>
+      </c>
       <c r="C14" t="n">
-        <v>17.53904</v>
+        <v>17.30806</v>
       </c>
       <c r="D14" t="n">
-        <v>17.34932</v>
+        <v>16.89093</v>
       </c>
       <c r="E14" t="n">
-        <v>18.00951</v>
+        <v>17.16641</v>
       </c>
       <c r="F14" t="n">
-        <v>44.39553</v>
+        <v>22.97043</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05328</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.87826</v>
+        <v>35.85284</v>
       </c>
     </row>
     <row r="15">
@@ -765,22 +775,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.80133</v>
+        <v>17.54836</v>
       </c>
       <c r="D15" t="n">
-        <v>17.27003</v>
+        <v>17.15281</v>
       </c>
       <c r="E15" t="n">
-        <v>17.57704</v>
+        <v>17.49969</v>
       </c>
       <c r="F15" t="n">
-        <v>45.27698</v>
+        <v>22.94508</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05337</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.94537</v>
+        <v>35.73909</v>
       </c>
     </row>
     <row r="16">
@@ -790,22 +797,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.76522</v>
+        <v>17.75217</v>
       </c>
       <c r="D16" t="n">
-        <v>17.83735</v>
+        <v>16.71197</v>
       </c>
       <c r="E16" t="n">
-        <v>17.77823</v>
+        <v>17.29395</v>
       </c>
       <c r="F16" t="n">
-        <v>45.41605</v>
+        <v>23.02912</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05338</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.99326</v>
+        <v>36.41681</v>
       </c>
     </row>
     <row r="17">
@@ -815,22 +819,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.6433</v>
+        <v>17.7619</v>
       </c>
       <c r="D17" t="n">
-        <v>17.544</v>
+        <v>16.96537</v>
       </c>
       <c r="E17" t="n">
-        <v>18.03306</v>
+        <v>17.24514</v>
       </c>
       <c r="F17" t="n">
-        <v>44.76364</v>
+        <v>23.52985</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05325</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.90559</v>
+        <v>36.4919</v>
       </c>
     </row>
     <row r="18">
@@ -840,22 +841,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.75401</v>
+        <v>17.50699</v>
       </c>
       <c r="D18" t="n">
-        <v>17.60759</v>
+        <v>16.92677</v>
       </c>
       <c r="E18" t="n">
-        <v>17.78253</v>
+        <v>17.38626</v>
       </c>
       <c r="F18" t="n">
-        <v>45.77662</v>
+        <v>22.36803</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05304</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.92124</v>
+        <v>37.1474</v>
       </c>
     </row>
     <row r="19">
@@ -865,22 +863,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.75276</v>
+        <v>17.43668</v>
       </c>
       <c r="D19" t="n">
-        <v>17.56253</v>
+        <v>17.06124</v>
       </c>
       <c r="E19" t="n">
-        <v>17.43966</v>
+        <v>17.34309</v>
       </c>
       <c r="F19" t="n">
-        <v>45.78672</v>
+        <v>23.21647</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05405</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.91313</v>
+        <v>36.02653</v>
       </c>
     </row>
     <row r="20">
@@ -890,22 +885,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18.03959</v>
+        <v>17.52817</v>
       </c>
       <c r="D20" t="n">
-        <v>17.29965</v>
+        <v>16.86745</v>
       </c>
       <c r="E20" t="n">
-        <v>17.6864</v>
+        <v>17.195</v>
       </c>
       <c r="F20" t="n">
-        <v>46.10563</v>
+        <v>23.26931</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05358</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.91896</v>
+        <v>35.98877</v>
       </c>
     </row>
   </sheetData>
